--- a/crates/agrafe-render/assets/probe/sheet.xlsx
+++ b/crates/agrafe-render/assets/probe/sheet.xlsx
@@ -35,5 +35,8 @@
       </c>
     </row>
   </sheetData>
+  <rowBreaks count="1" manualBreakCount="1">
+    <brk id="1" max="16383" man="1"/>
+  </rowBreaks>
 </worksheet>
 </file>